--- a/dcf/AWK.xlsx
+++ b/dcf/AWK.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1105,25 +1105,25 @@
         </is>
       </c>
       <c r="B4" s="52" t="n">
-        <v>0.06179875356046162</v>
+        <v>0.06169779232797624</v>
       </c>
       <c r="C4" s="52" t="n">
-        <v>0.06679875356046162</v>
+        <v>0.06669779232797625</v>
       </c>
       <c r="D4" s="52" t="n">
-        <v>0.07179875356046161</v>
+        <v>0.07169779232797624</v>
       </c>
       <c r="E4" s="52" t="n">
-        <v>0.07679875356046162</v>
+        <v>0.07669779232797624</v>
       </c>
       <c r="F4" s="52" t="n">
-        <v>0.08179875356046162</v>
+        <v>0.08169779232797625</v>
       </c>
       <c r="G4" s="52" t="n">
-        <v>0.08679875356046161</v>
+        <v>0.08669779232797624</v>
       </c>
       <c r="H4" s="52" t="n">
-        <v>0.09179875356046162</v>
+        <v>0.09169779232797624</v>
       </c>
     </row>
     <row r="5">
@@ -1131,25 +1131,25 @@
         <v>10</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>103.0791030133416</v>
+        <v>103.2366318363432</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>95.47625352856583</v>
+        <v>95.6259914166709</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>88.24851662636026</v>
+        <v>88.39088400378238</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>81.37569810250666</v>
+        <v>81.51109083929438</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>74.83878039938271</v>
+        <v>74.96757135249585</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>68.61984892777473</v>
+        <v>68.74238937882667</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>62.70202331769755</v>
+        <v>62.81864431473087</v>
       </c>
     </row>
     <row r="6">
@@ -1157,25 +1157,25 @@
         <v>11</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>117.3057166685437</v>
+        <v>117.4767799573534</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>109.0499662605706</v>
+        <v>109.2125569230016</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>101.202137237189</v>
+        <v>101.3567129822398</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>93.74024505283728</v>
+        <v>93.88723683618996</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>86.64358716625529</v>
+        <v>86.78340087040796</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>79.89266271548605</v>
+        <v>80.02568071717292</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>73.46909756914926</v>
+        <v>73.59568020208738</v>
       </c>
     </row>
     <row r="7">
@@ -1183,25 +1183,25 @@
         <v>12</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>131.5323303237458</v>
+        <v>131.7169280783636</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>122.6236789925753</v>
+        <v>122.7991224293322</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>114.1557578480177</v>
+        <v>114.3225419606971</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>106.1047920031679</v>
+        <v>106.2633828330855</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>98.44839393312786</v>
+        <v>98.59923038832005</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>91.16547650319738</v>
+        <v>91.30897205551919</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>84.23617182060096</v>
+        <v>84.37271608944388</v>
       </c>
     </row>
     <row r="8">
@@ -1209,25 +1209,25 @@
         <v>13</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>145.7589439789479</v>
-      </c>
-      <c r="C8" s="54" t="n">
-        <v>136.19739172458</v>
+        <v>145.9570761993738</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>136.3856879356628</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>127.1093784588465</v>
+        <v>127.2883709391545</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>118.4693389534985</v>
+        <v>118.6395288299811</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>110.2532007000004</v>
+        <v>110.4150599062321</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>102.4382902909087</v>
+        <v>102.5922633938655</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>95.00324607205266</v>
+        <v>95.14975197680039</v>
       </c>
     </row>
     <row r="9">
@@ -1235,25 +1235,25 @@
         <v>14</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>159.9855576341499</v>
+        <v>160.197224320384</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>149.7711044565847</v>
+        <v>149.9722534419934</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>140.0629990696752</v>
+        <v>140.2541999176119</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>130.8338859038291</v>
+        <v>131.0156748268766</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>122.058007466873</v>
+        <v>122.2308894241443</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>113.71110407862</v>
+        <v>113.8755547322117</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>105.7703203235043</v>
+        <v>105.9267878641569</v>
       </c>
     </row>
     <row r="10">
@@ -1261,25 +1261,25 @@
         <v>15</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>174.212171289352</v>
+        <v>174.4373724413942</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>163.3448171885893</v>
+        <v>163.5588189483241</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>153.016619680504</v>
+        <v>153.2200288960693</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>143.1984328541598</v>
+        <v>143.3918208237722</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>133.8628142337455</v>
+        <v>134.0467189420563</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>124.9839178663313</v>
+        <v>125.158846070558</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>116.537394574956</v>
+        <v>116.7038237515134</v>
       </c>
     </row>
     <row r="11">
@@ -1287,25 +1287,25 @@
         <v>16</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>188.438784944554</v>
+        <v>188.6775205624044</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>176.918529920594</v>
+        <v>177.1453844546547</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>165.9702402913327</v>
+        <v>166.1858578745266</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>155.5629798044904</v>
+        <v>155.7679668206677</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>145.6676210006181</v>
-      </c>
-      <c r="G11" s="54" t="n">
-        <v>136.2567316540426</v>
+        <v>145.8625484599685</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>136.4421374089042</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>127.3044688264077</v>
+        <v>127.4808596388699</v>
       </c>
     </row>
     <row r="13">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>136.8600006103516</v>
+        <v>135.8300018310547</v>
       </c>
     </row>
     <row r="14">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="B14" s="56" t="n">
-        <v>0.07679875356046162</v>
+        <v>0.07669779232797624</v>
       </c>
       <c r="C14" s="57" t="n">
         <v>13</v>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.9644901745651647</v>
+        <v>0.9645311679761804</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24410,7 +24410,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>136.8600006103516</v>
+        <v>135.8300018310547</v>
       </c>
     </row>
     <row r="49">
@@ -24572,13 +24572,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>118.4693389534985</v>
+        <v>118.6395288299811</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>192.2372122314825</v>
+        <v>192.4734039648237</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>61.19377802701045</v>
+        <v>61.31306034261458</v>
       </c>
     </row>
     <row r="59">
